--- a/Receivables Report/Receivables_Report_July_2026_H1.xlsx
+++ b/Receivables Report/Receivables_Report_July_2026_H1.xlsx
@@ -1303,7 +1303,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:14:46</t>
+    <t>2026-07-16 10:03:09</t>
   </si>
   <si>
     <t>Source</t>

--- a/Receivables Report/Receivables_Report_July_2026_H1.xlsx
+++ b/Receivables Report/Receivables_Report_July_2026_H1.xlsx
@@ -1303,7 +1303,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:09</t>
+    <t>2026-07-16 15:22:41</t>
   </si>
   <si>
     <t>Source</t>

--- a/Receivables Report/Receivables_Report_July_2026_H1.xlsx
+++ b/Receivables Report/Receivables_Report_July_2026_H1.xlsx
@@ -17,42 +17,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="336">
   <si>
     <t>Invoices (excl. void)</t>
   </si>
   <si>
-    <t>108</t>
+    <t>102</t>
   </si>
   <si>
     <t>Billed</t>
   </si>
   <si>
-    <t>9,279,111.84</t>
+    <t>1,406,146.13</t>
   </si>
   <si>
     <t>Collected</t>
   </si>
   <si>
-    <t>7,765,263.28</t>
+    <t>957,345.32</t>
   </si>
   <si>
     <t>Outstanding</t>
   </si>
   <si>
-    <t>1,513,848.56</t>
+    <t>448,800.81</t>
   </si>
   <si>
     <t>Collection rate</t>
   </si>
   <si>
-    <t>83.7%</t>
+    <t>68.1%</t>
   </si>
   <si>
     <t>Invoice</t>
   </si>
   <si>
-    <t>Visit</t>
+    <t>Job</t>
   </si>
   <si>
     <t>Customer</t>
@@ -79,145 +79,208 @@
     <t>IN0001</t>
   </si>
   <si>
-    <t>VI0001</t>
-  </si>
-  <si>
-    <t>CU0049</t>
-  </si>
-  <si>
-    <t>Elizabeth Wilson</t>
-  </si>
-  <si>
-    <t>QA-4461</t>
+    <t>JB0003</t>
+  </si>
+  <si>
+    <t>CU0014</t>
+  </si>
+  <si>
+    <t>Jason Wright</t>
+  </si>
+  <si>
+    <t>WP-2528</t>
+  </si>
+  <si>
+    <t>Partially paid</t>
+  </si>
+  <si>
+    <t>IN0002</t>
+  </si>
+  <si>
+    <t>JB0004</t>
+  </si>
+  <si>
+    <t>CU0005</t>
+  </si>
+  <si>
+    <t>Susan Peterson</t>
+  </si>
+  <si>
+    <t>PC-1931</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>IN0003</t>
+  </si>
+  <si>
+    <t>JB0005</t>
+  </si>
+  <si>
+    <t>CU0003</t>
+  </si>
+  <si>
+    <t>Rebecca Morgan</t>
+  </si>
+  <si>
+    <t>CAB-9379</t>
   </si>
   <si>
     <t>Settled</t>
   </si>
   <si>
-    <t>IN0002</t>
-  </si>
-  <si>
-    <t>VI0003</t>
-  </si>
-  <si>
-    <t>IN0003</t>
-  </si>
-  <si>
-    <t>VI0004</t>
-  </si>
-  <si>
-    <t>CU0003</t>
-  </si>
-  <si>
-    <t>Rebecca Morgan</t>
-  </si>
-  <si>
-    <t>CAP-6508</t>
-  </si>
-  <si>
     <t>IN0004</t>
   </si>
   <si>
-    <t>VI0005</t>
-  </si>
-  <si>
-    <t>CU0020</t>
-  </si>
-  <si>
-    <t>Richard Smith</t>
-  </si>
-  <si>
-    <t>CAP-3375</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
+    <t>JB0007</t>
+  </si>
+  <si>
+    <t>CU0021</t>
+  </si>
+  <si>
+    <t>Kenneth Harris</t>
+  </si>
+  <si>
+    <t>WP-2776</t>
   </si>
   <si>
     <t>IN0005</t>
   </si>
   <si>
-    <t>VI0006</t>
+    <t>JB0008</t>
+  </si>
+  <si>
+    <t>CU0010</t>
+  </si>
+  <si>
+    <t>Angela Miller</t>
+  </si>
+  <si>
+    <t>CAP-3200</t>
   </si>
   <si>
     <t>IN0006</t>
   </si>
   <si>
-    <t>VI0007</t>
-  </si>
-  <si>
-    <t>CU0054</t>
-  </si>
-  <si>
-    <t>David Collins</t>
-  </si>
-  <si>
-    <t>KB-2703</t>
+    <t>JB0010</t>
+  </si>
+  <si>
+    <t>CU0033</t>
+  </si>
+  <si>
+    <t>Sandra Peterson</t>
+  </si>
+  <si>
+    <t>CAP-1152</t>
   </si>
   <si>
     <t>IN0007</t>
   </si>
   <si>
-    <t>VI0008</t>
-  </si>
-  <si>
-    <t>CU0060</t>
-  </si>
-  <si>
-    <t>Jennifer Martin</t>
-  </si>
-  <si>
-    <t>PB-8071</t>
-  </si>
-  <si>
-    <t>Partially paid</t>
+    <t>JB0011</t>
+  </si>
+  <si>
+    <t>CU0001</t>
+  </si>
+  <si>
+    <t>Margaret Scott</t>
+  </si>
+  <si>
+    <t>CAB-3851</t>
   </si>
   <si>
     <t>IN0008</t>
   </si>
   <si>
-    <t>VI0009</t>
+    <t>JB0012</t>
+  </si>
+  <si>
+    <t>CU0027</t>
+  </si>
+  <si>
+    <t>Paul Cox</t>
+  </si>
+  <si>
+    <t>KB-5088</t>
   </si>
   <si>
     <t>IN0009</t>
   </si>
   <si>
-    <t>VI0012</t>
-  </si>
-  <si>
-    <t>CU0025</t>
-  </si>
-  <si>
-    <t>Elizabeth Reed</t>
-  </si>
-  <si>
-    <t>KA-5177</t>
+    <t>JB0013</t>
+  </si>
+  <si>
+    <t>BAC-3608</t>
   </si>
   <si>
     <t>IN0010</t>
   </si>
   <si>
-    <t>VI0013</t>
+    <t>JB0014</t>
+  </si>
+  <si>
+    <t>CU0034</t>
+  </si>
+  <si>
+    <t>Michael Cox</t>
+  </si>
+  <si>
+    <t>WP-6138</t>
   </si>
   <si>
     <t>IN0011</t>
   </si>
   <si>
-    <t>VI0015</t>
-  </si>
-  <si>
-    <t>CU0036</t>
-  </si>
-  <si>
-    <t>Mary Collins</t>
-  </si>
-  <si>
-    <t>QA-5247</t>
+    <t>JB0015</t>
+  </si>
+  <si>
+    <t>KB-1387</t>
   </si>
   <si>
     <t>IN0012</t>
   </si>
   <si>
-    <t>VI0016</t>
+    <t>JB0016</t>
+  </si>
+  <si>
+    <t>CU0016</t>
+  </si>
+  <si>
+    <t>Dorothy Jones</t>
+  </si>
+  <si>
+    <t>WP-3938</t>
+  </si>
+  <si>
+    <t>IN0013</t>
+  </si>
+  <si>
+    <t>JB0017</t>
+  </si>
+  <si>
+    <t>KA-8350</t>
+  </si>
+  <si>
+    <t>IN0014</t>
+  </si>
+  <si>
+    <t>JB0018</t>
+  </si>
+  <si>
+    <t>CU0035</t>
+  </si>
+  <si>
+    <t>Paul Green</t>
+  </si>
+  <si>
+    <t>PC-4111</t>
+  </si>
+  <si>
+    <t>IN0015</t>
+  </si>
+  <si>
+    <t>JB0019</t>
   </si>
   <si>
     <t>CU0018</t>
@@ -226,169 +289,187 @@
     <t>Matthew Stewart</t>
   </si>
   <si>
-    <t>KB-4573</t>
-  </si>
-  <si>
-    <t>IN0013</t>
-  </si>
-  <si>
-    <t>VI0017</t>
-  </si>
-  <si>
-    <t>CU0048</t>
-  </si>
-  <si>
-    <t>Betty Peterson</t>
-  </si>
-  <si>
-    <t>CAR-2705</t>
-  </si>
-  <si>
-    <t>IN0014</t>
-  </si>
-  <si>
-    <t>VI0018</t>
-  </si>
-  <si>
-    <t>IN0015</t>
-  </si>
-  <si>
-    <t>VI0019</t>
+    <t>KA-9004</t>
   </si>
   <si>
     <t>IN0016</t>
   </si>
   <si>
-    <t>VI0020</t>
-  </si>
-  <si>
-    <t>CU0058</t>
-  </si>
-  <si>
-    <t>Carol Ward</t>
-  </si>
-  <si>
-    <t>BAC-9888</t>
+    <t>JB0021</t>
   </si>
   <si>
     <t>IN0017</t>
   </si>
   <si>
-    <t>VI0021</t>
+    <t>JB0023</t>
   </si>
   <si>
     <t>IN0018</t>
   </si>
   <si>
-    <t>VI0022</t>
+    <t>JB0024</t>
   </si>
   <si>
     <t>IN0019</t>
   </si>
   <si>
-    <t>VI0023</t>
-  </si>
-  <si>
-    <t>CAR-1617</t>
+    <t>JB0025</t>
   </si>
   <si>
     <t>IN0020</t>
   </si>
   <si>
-    <t>VI0025</t>
-  </si>
-  <si>
-    <t>CU0042</t>
-  </si>
-  <si>
-    <t>Donald Wright</t>
-  </si>
-  <si>
-    <t>KA-4019</t>
+    <t>JB0026</t>
+  </si>
+  <si>
+    <t>KA-1128</t>
   </si>
   <si>
     <t>IN0021</t>
   </si>
   <si>
-    <t>VI0027</t>
-  </si>
-  <si>
-    <t>CU0038</t>
-  </si>
-  <si>
-    <t>Shirley Morgan</t>
-  </si>
-  <si>
-    <t>WP-3619</t>
+    <t>JB0027</t>
+  </si>
+  <si>
+    <t>CAR-9900</t>
   </si>
   <si>
     <t>IN0022</t>
   </si>
   <si>
-    <t>VI0028</t>
-  </si>
-  <si>
-    <t>CU0044</t>
-  </si>
-  <si>
-    <t>Amanda Hill</t>
-  </si>
-  <si>
-    <t>QA-6730</t>
+    <t>JB0028</t>
+  </si>
+  <si>
+    <t>CAB-1960</t>
   </si>
   <si>
     <t>IN0023</t>
   </si>
   <si>
-    <t>VI0029</t>
+    <t>JB0029</t>
+  </si>
+  <si>
+    <t>CU0028</t>
+  </si>
+  <si>
+    <t>Steven Cook</t>
+  </si>
+  <si>
+    <t>PC-9938</t>
   </si>
   <si>
     <t>IN0024</t>
   </si>
   <si>
-    <t>VI0030</t>
+    <t>JB0030</t>
   </si>
   <si>
     <t>IN0025</t>
   </si>
   <si>
-    <t>VI0032</t>
-  </si>
-  <si>
-    <t>CU0055</t>
-  </si>
-  <si>
-    <t>Brandon Carter</t>
-  </si>
-  <si>
-    <t>PC-3479</t>
+    <t>JB0031</t>
+  </si>
+  <si>
+    <t>KB-5351</t>
   </si>
   <si>
     <t>IN0026</t>
   </si>
   <si>
-    <t>VI0033</t>
-  </si>
-  <si>
-    <t>CU0053</t>
-  </si>
-  <si>
-    <t>Elizabeth Taylor</t>
-  </si>
-  <si>
-    <t>CAP-6263</t>
+    <t>JB0032</t>
+  </si>
+  <si>
+    <t>QA-6143</t>
   </si>
   <si>
     <t>IN0027</t>
   </si>
   <si>
-    <t>VI0034</t>
+    <t>JB0033</t>
+  </si>
+  <si>
+    <t>BAC-6753</t>
   </si>
   <si>
     <t>IN0028</t>
   </si>
   <si>
-    <t>VI0036</t>
+    <t>JB0034</t>
+  </si>
+  <si>
+    <t>QA-3532</t>
+  </si>
+  <si>
+    <t>IN0029</t>
+  </si>
+  <si>
+    <t>JB0035</t>
+  </si>
+  <si>
+    <t>IN0030</t>
+  </si>
+  <si>
+    <t>JB0036</t>
+  </si>
+  <si>
+    <t>IN0031</t>
+  </si>
+  <si>
+    <t>JB0037</t>
+  </si>
+  <si>
+    <t>IN0032</t>
+  </si>
+  <si>
+    <t>JB0038</t>
+  </si>
+  <si>
+    <t>CU0017</t>
+  </si>
+  <si>
+    <t>Anthony Miller</t>
+  </si>
+  <si>
+    <t>BAC-5616</t>
+  </si>
+  <si>
+    <t>IN0033</t>
+  </si>
+  <si>
+    <t>JB0039</t>
+  </si>
+  <si>
+    <t>IN0034</t>
+  </si>
+  <si>
+    <t>JB0040</t>
+  </si>
+  <si>
+    <t>CAP-8260</t>
+  </si>
+  <si>
+    <t>IN0035</t>
+  </si>
+  <si>
+    <t>JB0041</t>
+  </si>
+  <si>
+    <t>IN0036</t>
+  </si>
+  <si>
+    <t>JB0042</t>
+  </si>
+  <si>
+    <t>IN0037</t>
+  </si>
+  <si>
+    <t>JB0043</t>
+  </si>
+  <si>
+    <t>IN0038</t>
+  </si>
+  <si>
+    <t>JB0045</t>
   </si>
   <si>
     <t>CU0032</t>
@@ -397,361 +478,325 @@
     <t>Larry Allen</t>
   </si>
   <si>
-    <t>KA-4506</t>
-  </si>
-  <si>
-    <t>IN0029</t>
-  </si>
-  <si>
-    <t>VI0037</t>
-  </si>
-  <si>
-    <t>IN0030</t>
-  </si>
-  <si>
-    <t>VI0038</t>
-  </si>
-  <si>
-    <t>IN0031</t>
-  </si>
-  <si>
-    <t>VI0040</t>
-  </si>
-  <si>
-    <t>CU0034</t>
-  </si>
-  <si>
-    <t>Michael Cox</t>
-  </si>
-  <si>
-    <t>WP-5322</t>
-  </si>
-  <si>
-    <t>IN0032</t>
-  </si>
-  <si>
-    <t>VI0041</t>
-  </si>
-  <si>
-    <t>IN0033</t>
-  </si>
-  <si>
-    <t>VI0043</t>
-  </si>
-  <si>
-    <t>CU0047</t>
-  </si>
-  <si>
-    <t>Sandra Scott</t>
-  </si>
-  <si>
-    <t>WP-9521</t>
-  </si>
-  <si>
-    <t>IN0034</t>
-  </si>
-  <si>
-    <t>VI0044</t>
-  </si>
-  <si>
-    <t>CU0033</t>
-  </si>
-  <si>
-    <t>Sandra Peterson</t>
-  </si>
-  <si>
-    <t>PB-1742</t>
-  </si>
-  <si>
-    <t>IN0035</t>
-  </si>
-  <si>
-    <t>VI0045</t>
-  </si>
-  <si>
-    <t>IN0036</t>
-  </si>
-  <si>
-    <t>VI0046</t>
-  </si>
-  <si>
-    <t>PB-2406</t>
-  </si>
-  <si>
-    <t>IN0037</t>
-  </si>
-  <si>
-    <t>VI0047</t>
-  </si>
-  <si>
-    <t>IN0038</t>
-  </si>
-  <si>
-    <t>VI0048</t>
-  </si>
-  <si>
-    <t>CU0031</t>
-  </si>
-  <si>
-    <t>Paul Stewart</t>
-  </si>
-  <si>
-    <t>QA-8202</t>
+    <t>BAC-8454</t>
   </si>
   <si>
     <t>IN0039</t>
   </si>
   <si>
-    <t>VI0049</t>
-  </si>
-  <si>
-    <t>CU0045</t>
-  </si>
-  <si>
-    <t>Dorothy Lee</t>
-  </si>
-  <si>
-    <t>BAC-7244</t>
+    <t>JB0046</t>
   </si>
   <si>
     <t>IN0040</t>
   </si>
   <si>
-    <t>VI0051</t>
+    <t>JB0047</t>
+  </si>
+  <si>
+    <t>CU0004</t>
+  </si>
+  <si>
+    <t>Jonathan Nelson</t>
+  </si>
+  <si>
+    <t>CAP-8062</t>
   </si>
   <si>
     <t>IN0041</t>
   </si>
   <si>
-    <t>VI0054</t>
-  </si>
-  <si>
-    <t>CU0024</t>
-  </si>
-  <si>
-    <t>Matthew Wilson</t>
-  </si>
-  <si>
-    <t>BAC-2832</t>
+    <t>JB0048</t>
   </si>
   <si>
     <t>IN0042</t>
   </si>
   <si>
-    <t>VI0055</t>
-  </si>
-  <si>
-    <t>CU0050</t>
-  </si>
-  <si>
-    <t>William Rogers</t>
-  </si>
-  <si>
-    <t>KA-8234</t>
+    <t>JB0049</t>
+  </si>
+  <si>
+    <t>BAC-5700</t>
   </si>
   <si>
     <t>IN0043</t>
   </si>
   <si>
-    <t>VI0057</t>
-  </si>
-  <si>
-    <t>CU0051</t>
-  </si>
-  <si>
-    <t>Ruth Turner</t>
-  </si>
-  <si>
-    <t>PC-8772</t>
+    <t>JB0050</t>
   </si>
   <si>
     <t>IN0044</t>
   </si>
   <si>
-    <t>VI0059</t>
-  </si>
-  <si>
-    <t>PC-8285</t>
+    <t>JB0051</t>
   </si>
   <si>
     <t>IN0045</t>
   </si>
   <si>
-    <t>VI0060</t>
-  </si>
-  <si>
-    <t>PB-3711</t>
+    <t>JB0052</t>
   </si>
   <si>
     <t>IN0046</t>
   </si>
   <si>
-    <t>VI0061</t>
+    <t>JB0053</t>
   </si>
   <si>
     <t>IN0047</t>
   </si>
   <si>
-    <t>VI0063</t>
-  </si>
-  <si>
-    <t>CU0057</t>
-  </si>
-  <si>
-    <t>Betty Wood</t>
-  </si>
-  <si>
-    <t>KB-3146</t>
+    <t>JB0054</t>
   </si>
   <si>
     <t>IN0048</t>
   </si>
   <si>
-    <t>VI0064</t>
-  </si>
-  <si>
-    <t>CU0004</t>
-  </si>
-  <si>
-    <t>Jonathan Nelson</t>
-  </si>
-  <si>
-    <t>KB-1312</t>
+    <t>JB0055</t>
   </si>
   <si>
     <t>IN0049</t>
   </si>
   <si>
-    <t>VI0065</t>
-  </si>
-  <si>
-    <t>CU0019</t>
-  </si>
-  <si>
-    <t>Dorothy Collins</t>
-  </si>
-  <si>
-    <t>WP-4833</t>
+    <t>JB0057</t>
   </si>
   <si>
     <t>IN0050</t>
   </si>
   <si>
-    <t>VI0066</t>
+    <t>JB0058</t>
   </si>
   <si>
     <t>IN0051</t>
   </si>
   <si>
-    <t>VI0067</t>
-  </si>
-  <si>
-    <t>CU0027</t>
-  </si>
-  <si>
-    <t>Paul Cox</t>
-  </si>
-  <si>
-    <t>CAR-5728</t>
+    <t>JB0059</t>
+  </si>
+  <si>
+    <t>PB-1452</t>
   </si>
   <si>
     <t>IN0052</t>
   </si>
   <si>
-    <t>VI0069</t>
-  </si>
-  <si>
-    <t>CU0029</t>
-  </si>
-  <si>
-    <t>John Parker</t>
-  </si>
-  <si>
-    <t>PB-7510</t>
+    <t>JB0060</t>
   </si>
   <si>
     <t>IN0053</t>
   </si>
   <si>
-    <t>VI0070</t>
-  </si>
-  <si>
-    <t>KB-1556</t>
+    <t>JB0061</t>
   </si>
   <si>
     <t>IN0054</t>
   </si>
   <si>
-    <t>VI0071</t>
-  </si>
-  <si>
-    <t>CU0041</t>
-  </si>
-  <si>
-    <t>Larry Jackson</t>
-  </si>
-  <si>
-    <t>KA-5159</t>
+    <t>JB0062</t>
+  </si>
+  <si>
+    <t>CU0011</t>
+  </si>
+  <si>
+    <t>Anna Green</t>
+  </si>
+  <si>
+    <t>CAR-8238</t>
   </si>
   <si>
     <t>IN0055</t>
   </si>
   <si>
-    <t>VI0072</t>
+    <t>JB0063</t>
   </si>
   <si>
     <t>IN0056</t>
   </si>
   <si>
-    <t>VI0073</t>
-  </si>
-  <si>
-    <t>BAC-6901</t>
+    <t>JB0064</t>
   </si>
   <si>
     <t>IN0057</t>
   </si>
   <si>
-    <t>VI0074</t>
+    <t>JB0066</t>
   </si>
   <si>
     <t>IN0058</t>
   </si>
   <si>
-    <t>VI0075</t>
+    <t>JB0067</t>
   </si>
   <si>
     <t>IN0059</t>
   </si>
   <si>
-    <t>VI0076</t>
-  </si>
-  <si>
-    <t>CU0052</t>
-  </si>
-  <si>
-    <t>Shirley Howard</t>
-  </si>
-  <si>
-    <t>PC-9758</t>
+    <t>JB0068</t>
   </si>
   <si>
     <t>IN0060</t>
   </si>
   <si>
-    <t>VI0077</t>
+    <t>JB0070</t>
   </si>
   <si>
     <t>IN0061</t>
   </si>
   <si>
-    <t>VI0078</t>
+    <t>JB0071</t>
   </si>
   <si>
     <t>IN0062</t>
   </si>
   <si>
-    <t>VI0079</t>
+    <t>JB0073</t>
+  </si>
+  <si>
+    <t>IN0063</t>
+  </si>
+  <si>
+    <t>JB0074</t>
+  </si>
+  <si>
+    <t>IN0064</t>
+  </si>
+  <si>
+    <t>JB0076</t>
+  </si>
+  <si>
+    <t>IN0065</t>
+  </si>
+  <si>
+    <t>JB0077</t>
+  </si>
+  <si>
+    <t>IN0066</t>
+  </si>
+  <si>
+    <t>JB0080</t>
+  </si>
+  <si>
+    <t>IN0067</t>
+  </si>
+  <si>
+    <t>JB0081</t>
+  </si>
+  <si>
+    <t>PB-7592</t>
+  </si>
+  <si>
+    <t>IN0068</t>
+  </si>
+  <si>
+    <t>JB0082</t>
+  </si>
+  <si>
+    <t>IN0069</t>
+  </si>
+  <si>
+    <t>JB0083</t>
+  </si>
+  <si>
+    <t>CU0013</t>
+  </si>
+  <si>
+    <t>Mark Johnson</t>
+  </si>
+  <si>
+    <t>CAP-1993</t>
+  </si>
+  <si>
+    <t>IN0070</t>
+  </si>
+  <si>
+    <t>JB0084</t>
+  </si>
+  <si>
+    <t>IN0071</t>
+  </si>
+  <si>
+    <t>JB0085</t>
+  </si>
+  <si>
+    <t>CU0015</t>
+  </si>
+  <si>
+    <t>Donald Mitchell</t>
+  </si>
+  <si>
+    <t>CAR-4644</t>
+  </si>
+  <si>
+    <t>IN0072</t>
+  </si>
+  <si>
+    <t>JB0086</t>
+  </si>
+  <si>
+    <t>IN0073</t>
+  </si>
+  <si>
+    <t>JB0088</t>
+  </si>
+  <si>
+    <t>IN0074</t>
+  </si>
+  <si>
+    <t>JB0089</t>
+  </si>
+  <si>
+    <t>IN0075</t>
+  </si>
+  <si>
+    <t>JB0090</t>
+  </si>
+  <si>
+    <t>IN0076</t>
+  </si>
+  <si>
+    <t>JB0092</t>
+  </si>
+  <si>
+    <t>IN0077</t>
+  </si>
+  <si>
+    <t>JB0093</t>
+  </si>
+  <si>
+    <t>IN0078</t>
+  </si>
+  <si>
+    <t>JB0095</t>
+  </si>
+  <si>
+    <t>IN0079</t>
+  </si>
+  <si>
+    <t>JB0098</t>
+  </si>
+  <si>
+    <t>IN0080</t>
+  </si>
+  <si>
+    <t>JB0099</t>
+  </si>
+  <si>
+    <t>KB-7615</t>
+  </si>
+  <si>
+    <t>IN0081</t>
+  </si>
+  <si>
+    <t>JB0100</t>
+  </si>
+  <si>
+    <t>IN0082</t>
+  </si>
+  <si>
+    <t>JB0102</t>
+  </si>
+  <si>
+    <t>IN0083</t>
+  </si>
+  <si>
+    <t>JB0103</t>
   </si>
   <si>
     <t>CU0022</t>
@@ -760,469 +805,127 @@
     <t>Melissa Moore</t>
   </si>
   <si>
-    <t>KA-7111</t>
-  </si>
-  <si>
-    <t>IN0063</t>
-  </si>
-  <si>
-    <t>VI0080</t>
-  </si>
-  <si>
-    <t>CU0030</t>
-  </si>
-  <si>
-    <t>Rebecca Walker</t>
-  </si>
-  <si>
-    <t>QA-5387</t>
-  </si>
-  <si>
-    <t>IN0064</t>
-  </si>
-  <si>
-    <t>VI0082</t>
-  </si>
-  <si>
-    <t>CU0005</t>
-  </si>
-  <si>
-    <t>Susan Peterson</t>
-  </si>
-  <si>
-    <t>BAC-4650</t>
-  </si>
-  <si>
-    <t>IN0065</t>
-  </si>
-  <si>
-    <t>VI0083</t>
-  </si>
-  <si>
-    <t>CU0026</t>
-  </si>
-  <si>
-    <t>David Harris</t>
-  </si>
-  <si>
-    <t>KA-2826</t>
-  </si>
-  <si>
-    <t>IN0066</t>
-  </si>
-  <si>
-    <t>VI0084</t>
-  </si>
-  <si>
-    <t>IN0067</t>
-  </si>
-  <si>
-    <t>VI0085</t>
-  </si>
-  <si>
-    <t>CU0059</t>
-  </si>
-  <si>
-    <t>Donald Wilson</t>
-  </si>
-  <si>
-    <t>PC-6419</t>
-  </si>
-  <si>
-    <t>IN0068</t>
-  </si>
-  <si>
-    <t>VI0086</t>
-  </si>
-  <si>
-    <t>IN0069</t>
-  </si>
-  <si>
-    <t>VI0087</t>
-  </si>
-  <si>
-    <t>PB-8784</t>
-  </si>
-  <si>
-    <t>IN0070</t>
-  </si>
-  <si>
-    <t>VI0088</t>
-  </si>
-  <si>
-    <t>CU0010</t>
-  </si>
-  <si>
-    <t>Angela Miller</t>
-  </si>
-  <si>
-    <t>PB-6840</t>
-  </si>
-  <si>
-    <t>IN0071</t>
-  </si>
-  <si>
-    <t>VI0089</t>
-  </si>
-  <si>
-    <t>IN0072</t>
-  </si>
-  <si>
-    <t>VI0090</t>
-  </si>
-  <si>
-    <t>PB-4567</t>
-  </si>
-  <si>
-    <t>IN0073</t>
-  </si>
-  <si>
-    <t>VI0091</t>
-  </si>
-  <si>
-    <t>IN0074</t>
-  </si>
-  <si>
-    <t>VI0092</t>
-  </si>
-  <si>
-    <t>KA-3844</t>
-  </si>
-  <si>
-    <t>IN0075</t>
-  </si>
-  <si>
-    <t>VI0093</t>
-  </si>
-  <si>
-    <t>IN0076</t>
-  </si>
-  <si>
-    <t>VI0094</t>
-  </si>
-  <si>
-    <t>IN0077</t>
-  </si>
-  <si>
-    <t>VI0095</t>
-  </si>
-  <si>
-    <t>CU0012</t>
-  </si>
-  <si>
-    <t>Richard Roberts</t>
-  </si>
-  <si>
-    <t>PC-3907</t>
-  </si>
-  <si>
-    <t>IN0078</t>
-  </si>
-  <si>
-    <t>VI0096</t>
-  </si>
-  <si>
-    <t>IN0079</t>
-  </si>
-  <si>
-    <t>VI0097</t>
-  </si>
-  <si>
-    <t>CU0014</t>
-  </si>
-  <si>
-    <t>Jason Wright</t>
-  </si>
-  <si>
-    <t>QA-3052</t>
-  </si>
-  <si>
-    <t>IN0080</t>
-  </si>
-  <si>
-    <t>VI0098</t>
-  </si>
-  <si>
-    <t>IN0081</t>
-  </si>
-  <si>
-    <t>VI0099</t>
-  </si>
-  <si>
-    <t>BAC-9854</t>
-  </si>
-  <si>
-    <t>IN0082</t>
-  </si>
-  <si>
-    <t>VI0100</t>
-  </si>
-  <si>
-    <t>IN0083</t>
-  </si>
-  <si>
-    <t>VI0101</t>
-  </si>
-  <si>
-    <t>PB-7640</t>
+    <t>CAB-1027</t>
   </si>
   <si>
     <t>IN0084</t>
   </si>
   <si>
-    <t>VI0102</t>
-  </si>
-  <si>
-    <t>CU0016</t>
-  </si>
-  <si>
-    <t>Dorothy Jones</t>
-  </si>
-  <si>
-    <t>PB-8656</t>
+    <t>JB0104</t>
   </si>
   <si>
     <t>IN0085</t>
   </si>
   <si>
-    <t>VI0103</t>
+    <t>JB0105</t>
   </si>
   <si>
     <t>IN0086</t>
   </si>
   <si>
-    <t>VI0106</t>
-  </si>
-  <si>
-    <t>CAP-9738</t>
+    <t>JB0106</t>
+  </si>
+  <si>
+    <t>PC-1685</t>
   </si>
   <si>
     <t>IN0087</t>
   </si>
   <si>
-    <t>VI0107</t>
+    <t>JB0107</t>
   </si>
   <si>
     <t>IN0088</t>
   </si>
   <si>
-    <t>VI0108</t>
-  </si>
-  <si>
-    <t>CU0023</t>
-  </si>
-  <si>
-    <t>Anna Martin</t>
-  </si>
-  <si>
-    <t>CAB-6824</t>
+    <t>JB0108</t>
   </si>
   <si>
     <t>IN0089</t>
   </si>
   <si>
-    <t>VI0110</t>
+    <t>JB0109</t>
   </si>
   <si>
     <t>IN0090</t>
   </si>
   <si>
-    <t>VI0111</t>
-  </si>
-  <si>
-    <t>CU0043</t>
-  </si>
-  <si>
-    <t>Edward Ward</t>
-  </si>
-  <si>
-    <t>KB-8975</t>
+    <t>JB0110</t>
   </si>
   <si>
     <t>IN0091</t>
   </si>
   <si>
-    <t>VI0112</t>
+    <t>JB0112</t>
   </si>
   <si>
     <t>IN0092</t>
   </si>
   <si>
-    <t>VI0114</t>
-  </si>
-  <si>
-    <t>CAB-2708</t>
+    <t>JB0113</t>
   </si>
   <si>
     <t>IN0093</t>
   </si>
   <si>
-    <t>VI0115</t>
-  </si>
-  <si>
-    <t>CU0001</t>
-  </si>
-  <si>
-    <t>Margaret Scott</t>
-  </si>
-  <si>
-    <t>WP-8361</t>
+    <t>JB0114</t>
+  </si>
+  <si>
+    <t>QA-2343</t>
   </si>
   <si>
     <t>IN0094</t>
   </si>
   <si>
-    <t>VI0116</t>
+    <t>JB0115</t>
   </si>
   <si>
     <t>IN0095</t>
   </si>
   <si>
-    <t>VI0117</t>
+    <t>JB0116</t>
   </si>
   <si>
     <t>IN0096</t>
   </si>
   <si>
-    <t>VI0118</t>
-  </si>
-  <si>
-    <t>CU0037</t>
-  </si>
-  <si>
-    <t>Laura Wilson</t>
-  </si>
-  <si>
-    <t>BAC-7924</t>
+    <t>JB0118</t>
   </si>
   <si>
     <t>IN0097</t>
   </si>
   <si>
-    <t>VI0119</t>
+    <t>JB0121</t>
   </si>
   <si>
     <t>IN0098</t>
   </si>
   <si>
-    <t>VI0120</t>
-  </si>
-  <si>
-    <t>BAC-6641</t>
+    <t>JB0122</t>
   </si>
   <si>
     <t>IN0099</t>
   </si>
   <si>
-    <t>VI0121</t>
-  </si>
-  <si>
-    <t>CU0040</t>
-  </si>
-  <si>
-    <t>William Allen</t>
-  </si>
-  <si>
-    <t>PB-7791</t>
+    <t>JB0123</t>
   </si>
   <si>
     <t>IN0100</t>
   </si>
   <si>
-    <t>VI0122</t>
-  </si>
-  <si>
-    <t>CU0028</t>
-  </si>
-  <si>
-    <t>Steven Cook</t>
-  </si>
-  <si>
-    <t>CAR-7656</t>
+    <t>JB0124</t>
   </si>
   <si>
     <t>IN0101</t>
   </si>
   <si>
-    <t>VI0123</t>
-  </si>
-  <si>
-    <t>CU0008</t>
-  </si>
-  <si>
-    <t>Pamela Howard</t>
-  </si>
-  <si>
-    <t>PC-6492</t>
+    <t>JB0125</t>
   </si>
   <si>
     <t>IN0102</t>
   </si>
   <si>
-    <t>VI0124</t>
-  </si>
-  <si>
-    <t>CAP-1833</t>
-  </si>
-  <si>
-    <t>IN0103</t>
-  </si>
-  <si>
-    <t>VI0125</t>
-  </si>
-  <si>
-    <t>CAP-5873</t>
-  </si>
-  <si>
-    <t>IN0104</t>
-  </si>
-  <si>
-    <t>VI0126</t>
-  </si>
-  <si>
-    <t>IN0105</t>
-  </si>
-  <si>
-    <t>VI0127</t>
-  </si>
-  <si>
-    <t>KB-5027</t>
-  </si>
-  <si>
-    <t>IN0106</t>
-  </si>
-  <si>
-    <t>VI0128</t>
-  </si>
-  <si>
-    <t>IN0107</t>
-  </si>
-  <si>
-    <t>VI0129</t>
-  </si>
-  <si>
-    <t>CU0035</t>
-  </si>
-  <si>
-    <t>Paul Green</t>
-  </si>
-  <si>
-    <t>CAP-4919</t>
-  </si>
-  <si>
-    <t>IN0108</t>
-  </si>
-  <si>
-    <t>VI0130</t>
-  </si>
-  <si>
-    <t>CU0015</t>
-  </si>
-  <si>
-    <t>Donald Mitchell</t>
-  </si>
-  <si>
-    <t>KA-2556</t>
+    <t>JB0127</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1237,15 +940,6 @@
     <t>0-30 days</t>
   </si>
   <si>
-    <t>31-60 days</t>
-  </si>
-  <si>
-    <t>61-90 days</t>
-  </si>
-  <si>
-    <t>90+ days</t>
-  </si>
-  <si>
     <t>Method</t>
   </si>
   <si>
@@ -1255,18 +949,18 @@
     <t>Amount</t>
   </si>
   <si>
+    <t>Bank Transfer</t>
+  </si>
+  <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>Bank Transfer</t>
+    <t>Cheque</t>
   </si>
   <si>
     <t>Card</t>
   </si>
   <si>
-    <t>Cheque</t>
-  </si>
-  <si>
     <t>Recorded Status</t>
   </si>
   <si>
@@ -1297,13 +991,13 @@
     <t>Snapshot taken (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16</t>
+    <t>2026-07-23</t>
   </si>
   <si>
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 15:22:41</t>
+    <t>2026-07-23 07:38:15</t>
   </si>
   <si>
     <t>Source</t>
@@ -1457,18 +1151,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.58984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.50390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.5078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="16.6640625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="10.1796875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="11.69921875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.78515625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.99609375" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="13.02734375" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="12.3125" customWidth="true" bestFit="true"/>
   </cols>
@@ -1525,22 +1219,22 @@
         <v>23</v>
       </c>
       <c r="F2" t="n" s="5">
-        <v>45848.0</v>
+        <v>46206.0</v>
       </c>
       <c r="G2" t="n" s="2">
-        <v>71069.0</v>
+        <v>18521.96</v>
       </c>
       <c r="H2" t="n" s="2">
-        <v>71069.0</v>
+        <v>8943.24</v>
       </c>
       <c r="I2" t="n" s="2">
-        <v>0.0</v>
+        <v>9578.72</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>371.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="3">
@@ -1551,941 +1245,917 @@
         <v>26</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n" s="5">
-        <v>46155.0</v>
+        <v>46206.0</v>
       </c>
       <c r="G3" t="n" s="2">
-        <v>8743.95</v>
+        <v>22365.7</v>
       </c>
       <c r="H3" t="n" s="2">
-        <v>8743.95</v>
+        <v>0.0</v>
       </c>
       <c r="I3" t="n" s="2">
-        <v>0.0</v>
+        <v>22365.7</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>64.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n" s="5">
-        <v>45959.0</v>
+        <v>46206.0</v>
       </c>
       <c r="G4" t="n" s="2">
-        <v>156647.21</v>
+        <v>4791.25</v>
       </c>
       <c r="H4" t="n" s="2">
-        <v>156647.21</v>
+        <v>4791.25</v>
       </c>
       <c r="I4" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>260.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n" s="5">
-        <v>46164.0</v>
+        <v>46206.0</v>
       </c>
       <c r="G5" t="n" s="2">
-        <v>97472.55</v>
+        <v>12917.51</v>
       </c>
       <c r="H5" t="n" s="2">
-        <v>0.0</v>
+        <v>6846.53</v>
       </c>
       <c r="I5" t="n" s="2">
-        <v>97472.55</v>
+        <v>6070.98</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>55.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n" s="5">
-        <v>45742.0</v>
+        <v>46206.0</v>
       </c>
       <c r="G6" t="n" s="2">
-        <v>23191.6</v>
+        <v>3782.12</v>
       </c>
       <c r="H6" t="n" s="2">
-        <v>23191.6</v>
+        <v>3782.12</v>
       </c>
       <c r="I6" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>477.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n" s="5">
-        <v>45962.0</v>
+        <v>46207.0</v>
       </c>
       <c r="G7" t="n" s="2">
-        <v>208499.52</v>
+        <v>11562.81</v>
       </c>
       <c r="H7" t="n" s="2">
-        <v>208499.52</v>
+        <v>4581.48</v>
       </c>
       <c r="I7" t="n" s="2">
-        <v>0.0</v>
+        <v>6981.33</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>257.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n" s="5">
-        <v>45939.0</v>
+        <v>46207.0</v>
       </c>
       <c r="G8" t="n" s="2">
-        <v>83557.01</v>
+        <v>10748.76</v>
       </c>
       <c r="H8" t="n" s="2">
-        <v>41153.63</v>
+        <v>10748.76</v>
       </c>
       <c r="I8" t="n" s="2">
-        <v>42403.38</v>
+        <v>0.0</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n" s="0">
-        <v>280.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n" s="5">
-        <v>45817.0</v>
+        <v>46207.0</v>
       </c>
       <c r="G9" t="n" s="2">
-        <v>124457.24</v>
+        <v>20396.97</v>
       </c>
       <c r="H9" t="n" s="2">
-        <v>124457.24</v>
+        <v>20396.97</v>
       </c>
       <c r="I9" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n" s="0">
-        <v>402.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>56</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C10" s="0"/>
+      <c r="D10" s="0"/>
       <c r="E10" t="s" s="0">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n" s="5">
-        <v>45782.0</v>
+        <v>46207.0</v>
       </c>
       <c r="G10" t="n" s="2">
-        <v>177713.07</v>
+        <v>20357.27</v>
       </c>
       <c r="H10" t="n" s="2">
-        <v>177713.07</v>
+        <v>20357.27</v>
       </c>
       <c r="I10" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n" s="0">
-        <v>437.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n" s="5">
-        <v>45719.0</v>
+        <v>46207.0</v>
       </c>
       <c r="G11" t="n" s="2">
-        <v>32415.36</v>
+        <v>17248.99</v>
       </c>
       <c r="H11" t="n" s="2">
-        <v>0.0</v>
+        <v>17248.99</v>
       </c>
       <c r="I11" t="n" s="2">
-        <v>32415.36</v>
+        <v>0.0</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n" s="0">
-        <v>500.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n" s="5">
-        <v>45997.0</v>
+        <v>46208.0</v>
       </c>
       <c r="G12" t="n" s="2">
-        <v>7683.09</v>
+        <v>12458.08</v>
       </c>
       <c r="H12" t="n" s="2">
-        <v>7683.09</v>
+        <v>12458.08</v>
       </c>
       <c r="I12" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n" s="0">
-        <v>222.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n" s="5">
-        <v>46009.0</v>
+        <v>46208.0</v>
       </c>
       <c r="G13" t="n" s="2">
-        <v>28262.86</v>
+        <v>3197.97</v>
       </c>
       <c r="H13" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="I13" t="n" s="2">
-        <v>28262.86</v>
+        <v>3197.97</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K13" t="n" s="0">
-        <v>210.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n" s="5">
-        <v>45901.0</v>
+        <v>46208.0</v>
       </c>
       <c r="G14" t="n" s="2">
-        <v>10742.49</v>
+        <v>2468.74</v>
       </c>
       <c r="H14" t="n" s="2">
-        <v>10742.49</v>
+        <v>2468.74</v>
       </c>
       <c r="I14" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K14" t="n" s="0">
-        <v>318.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n" s="5">
-        <v>45725.0</v>
+        <v>46208.0</v>
       </c>
       <c r="G15" t="n" s="2">
-        <v>79251.84</v>
+        <v>10484.59</v>
       </c>
       <c r="H15" t="n" s="2">
-        <v>79251.84</v>
+        <v>10484.59</v>
       </c>
       <c r="I15" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n" s="0">
-        <v>494.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n" s="5">
-        <v>45840.0</v>
+        <v>46208.0</v>
       </c>
       <c r="G16" t="n" s="2">
-        <v>63543.87</v>
+        <v>22884.6</v>
       </c>
       <c r="H16" t="n" s="2">
-        <v>63543.87</v>
+        <v>22884.6</v>
       </c>
       <c r="I16" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n" s="0">
-        <v>379.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n" s="5">
-        <v>46180.0</v>
+        <v>46209.0</v>
       </c>
       <c r="G17" t="n" s="2">
-        <v>48637.31</v>
+        <v>10523.13</v>
       </c>
       <c r="H17" t="n" s="2">
-        <v>48637.31</v>
+        <v>6251.53</v>
       </c>
       <c r="I17" t="n" s="2">
-        <v>0.0</v>
+        <v>4271.6</v>
       </c>
       <c r="J17" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K17" t="n" s="0">
-        <v>39.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n" s="5">
-        <v>45859.0</v>
+        <v>46209.0</v>
       </c>
       <c r="G18" t="n" s="2">
-        <v>129275.86</v>
+        <v>8211.9</v>
       </c>
       <c r="H18" t="n" s="2">
-        <v>129275.86</v>
+        <v>8211.9</v>
       </c>
       <c r="I18" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n" s="0">
-        <v>360.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>82</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
       <c r="E19" t="s" s="0">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n" s="5">
-        <v>45926.0</v>
+        <v>46209.0</v>
       </c>
       <c r="G19" t="n" s="2">
-        <v>86018.34</v>
+        <v>23496.3</v>
       </c>
       <c r="H19" t="n" s="2">
-        <v>86018.34</v>
+        <v>23496.3</v>
       </c>
       <c r="I19" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n" s="0">
-        <v>293.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n" s="5">
-        <v>45995.0</v>
+        <v>46210.0</v>
       </c>
       <c r="G20" t="n" s="2">
-        <v>42154.81</v>
+        <v>9475.33</v>
       </c>
       <c r="H20" t="n" s="2">
-        <v>42154.81</v>
+        <v>0.0</v>
       </c>
       <c r="I20" t="n" s="2">
-        <v>0.0</v>
+        <v>9475.33</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n" s="0">
-        <v>224.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>94</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
       <c r="E21" t="s" s="0">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n" s="5">
-        <v>45840.0</v>
+        <v>46210.0</v>
       </c>
       <c r="G21" t="n" s="2">
-        <v>60122.89</v>
+        <v>8354.18</v>
       </c>
       <c r="H21" t="n" s="2">
-        <v>35763.68</v>
+        <v>5783.83</v>
       </c>
       <c r="I21" t="n" s="2">
-        <v>24359.21</v>
+        <v>2570.35</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>379.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s" s="0">
-        <v>99</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C22" s="0"/>
+      <c r="D22" s="0"/>
       <c r="E22" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F22" t="n" s="5">
-        <v>46126.0</v>
+        <v>46210.0</v>
       </c>
       <c r="G22" t="n" s="2">
-        <v>157703.98</v>
+        <v>17884.01</v>
       </c>
       <c r="H22" t="n" s="2">
-        <v>157703.98</v>
+        <v>11170.34</v>
       </c>
       <c r="I22" t="n" s="2">
-        <v>0.0</v>
+        <v>6713.67</v>
       </c>
       <c r="J22" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K22" t="n" s="0">
-        <v>93.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>102</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>104</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C23" s="0"/>
+      <c r="D23" s="0"/>
       <c r="E23" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n" s="5">
-        <v>45813.0</v>
+        <v>46210.0</v>
       </c>
       <c r="G23" t="n" s="2">
-        <v>54121.37</v>
+        <v>17271.08</v>
       </c>
       <c r="H23" t="n" s="2">
-        <v>54121.37</v>
+        <v>11700.16</v>
       </c>
       <c r="I23" t="n" s="2">
-        <v>0.0</v>
+        <v>5570.92</v>
       </c>
       <c r="J23" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K23" t="n" s="0">
-        <v>406.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F24" t="n" s="5">
-        <v>45871.0</v>
+        <v>46210.0</v>
       </c>
       <c r="G24" t="n" s="2">
-        <v>140949.87</v>
+        <v>9052.33</v>
       </c>
       <c r="H24" t="n" s="2">
-        <v>140949.87</v>
+        <v>9052.33</v>
       </c>
       <c r="I24" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n" s="0">
-        <v>348.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F25" t="n" s="5">
-        <v>46048.0</v>
+        <v>46211.0</v>
       </c>
       <c r="G25" t="n" s="2">
-        <v>42980.42</v>
+        <v>8359.49</v>
       </c>
       <c r="H25" t="n" s="2">
-        <v>0.0</v>
+        <v>5469.75</v>
       </c>
       <c r="I25" t="n" s="2">
-        <v>42980.42</v>
+        <v>2889.74</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n" s="0">
-        <v>171.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F26" t="n" s="5">
-        <v>45898.0</v>
+        <v>46211.0</v>
       </c>
       <c r="G26" t="n" s="2">
-        <v>137537.59</v>
+        <v>18284.43</v>
       </c>
       <c r="H26" t="n" s="2">
-        <v>137537.59</v>
+        <v>0.0</v>
       </c>
       <c r="I26" t="n" s="2">
-        <v>0.0</v>
+        <v>18284.43</v>
       </c>
       <c r="J26" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K26" t="n" s="0">
-        <v>321.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F27" t="n" s="5">
-        <v>46205.0</v>
+        <v>46211.0</v>
       </c>
       <c r="G27" t="n" s="2">
-        <v>50158.57</v>
+        <v>4359.52</v>
       </c>
       <c r="H27" t="n" s="2">
-        <v>50158.57</v>
+        <v>4359.52</v>
       </c>
       <c r="I27" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n" s="0">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F28" t="n" s="5">
-        <v>45985.0</v>
+        <v>46211.0</v>
       </c>
       <c r="G28" t="n" s="2">
-        <v>84116.18</v>
+        <v>23644.46</v>
       </c>
       <c r="H28" t="n" s="2">
-        <v>84116.18</v>
+        <v>23644.46</v>
       </c>
       <c r="I28" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n" s="0">
-        <v>234.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="D29" t="s" s="0">
         <v>125</v>
       </c>
+      <c r="C29" s="0"/>
+      <c r="D29" s="0"/>
       <c r="E29" t="s" s="0">
         <v>126</v>
       </c>
       <c r="F29" t="n" s="5">
-        <v>46007.0</v>
+        <v>46211.0</v>
       </c>
       <c r="G29" t="n" s="2">
-        <v>58692.52</v>
+        <v>5489.72</v>
       </c>
       <c r="H29" t="n" s="2">
-        <v>58692.52</v>
+        <v>5489.72</v>
       </c>
       <c r="I29" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J29" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n" s="0">
-        <v>212.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="30">
@@ -2496,31 +2166,31 @@
         <v>128</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="F30" t="n" s="5">
-        <v>45796.0</v>
+        <v>46212.0</v>
       </c>
       <c r="G30" t="n" s="2">
-        <v>116178.33</v>
+        <v>22895.6</v>
       </c>
       <c r="H30" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="I30" t="n" s="2">
-        <v>116178.33</v>
+        <v>22895.6</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K30" t="n" s="0">
-        <v>423.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="31">
@@ -2531,31 +2201,31 @@
         <v>130</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n" s="5">
-        <v>46013.0</v>
+        <v>46212.0</v>
       </c>
       <c r="G31" t="n" s="2">
-        <v>153468.37</v>
+        <v>23794.57</v>
       </c>
       <c r="H31" t="n" s="2">
-        <v>153468.37</v>
+        <v>23794.57</v>
       </c>
       <c r="I31" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n" s="0">
-        <v>206.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="32">
@@ -2565,67 +2235,63 @@
       <c r="B32" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="C32" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="D32" t="s" s="0">
-        <v>134</v>
-      </c>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
       <c r="E32" t="s" s="0">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F32" t="n" s="5">
-        <v>46124.0</v>
+        <v>46212.0</v>
       </c>
       <c r="G32" t="n" s="2">
-        <v>162287.47</v>
+        <v>2061.54</v>
       </c>
       <c r="H32" t="n" s="2">
-        <v>162287.47</v>
+        <v>978.78</v>
       </c>
       <c r="I32" t="n" s="2">
-        <v>0.0</v>
+        <v>1082.76</v>
       </c>
       <c r="J32" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K32" t="n" s="0">
-        <v>95.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s" s="0">
         <v>136</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="E33" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="C33" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="D33" t="s" s="0">
-        <v>134</v>
-      </c>
-      <c r="E33" t="s" s="0">
-        <v>135</v>
-      </c>
       <c r="F33" t="n" s="5">
-        <v>46072.0</v>
+        <v>46212.0</v>
       </c>
       <c r="G33" t="n" s="2">
-        <v>228682.06</v>
+        <v>21770.95</v>
       </c>
       <c r="H33" t="n" s="2">
-        <v>228682.06</v>
+        <v>14322.13</v>
       </c>
       <c r="I33" t="n" s="2">
-        <v>0.0</v>
+        <v>7448.82</v>
       </c>
       <c r="J33" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K33" t="n" s="0">
-        <v>147.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="34">
@@ -2636,2670 +2302,2416 @@
         <v>139</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="F34" t="n" s="5">
-        <v>45935.0</v>
+        <v>46213.0</v>
       </c>
       <c r="G34" t="n" s="2">
-        <v>145562.77</v>
+        <v>16895.6</v>
       </c>
       <c r="H34" t="n" s="2">
-        <v>31749.21</v>
+        <v>16895.6</v>
       </c>
       <c r="I34" t="n" s="2">
-        <v>113813.56</v>
+        <v>0.0</v>
       </c>
       <c r="J34" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n" s="0">
-        <v>284.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F35" t="n" s="5">
-        <v>46176.0</v>
+        <v>46213.0</v>
       </c>
       <c r="G35" t="n" s="2">
-        <v>150149.37</v>
+        <v>23187.43</v>
       </c>
       <c r="H35" t="n" s="2">
-        <v>150149.37</v>
+        <v>23187.43</v>
       </c>
       <c r="I35" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J35" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K35" t="n" s="0">
-        <v>43.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="F36" t="n" s="5">
-        <v>45975.0</v>
+        <v>46213.0</v>
       </c>
       <c r="G36" t="n" s="2">
-        <v>223148.95</v>
+        <v>13357.29</v>
       </c>
       <c r="H36" t="n" s="2">
-        <v>223148.95</v>
+        <v>13357.29</v>
       </c>
       <c r="I36" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J36" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n" s="0">
-        <v>244.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="C37" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s" s="0">
-        <v>56</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C37" s="0"/>
+      <c r="D37" s="0"/>
       <c r="E37" t="s" s="0">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="F37" t="n" s="5">
-        <v>46217.0</v>
+        <v>46213.0</v>
       </c>
       <c r="G37" t="n" s="2">
-        <v>218085.19</v>
+        <v>7265.26</v>
       </c>
       <c r="H37" t="n" s="2">
-        <v>218085.19</v>
+        <v>0.0</v>
       </c>
       <c r="I37" t="n" s="2">
-        <v>0.0</v>
+        <v>7265.26</v>
       </c>
       <c r="J37" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K37" t="n" s="0">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s" s="0">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n" s="5">
-        <v>45982.0</v>
+        <v>46213.0</v>
       </c>
       <c r="G38" t="n" s="2">
-        <v>31577.51</v>
+        <v>13936.17</v>
       </c>
       <c r="H38" t="n" s="2">
-        <v>31577.51</v>
+        <v>4620.83</v>
       </c>
       <c r="I38" t="n" s="2">
-        <v>0.0</v>
+        <v>9315.34</v>
       </c>
       <c r="J38" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K38" t="n" s="0">
-        <v>237.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F39" t="n" s="5">
-        <v>45711.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G39" t="n" s="2">
-        <v>67212.63</v>
+        <v>17239.42</v>
       </c>
       <c r="H39" t="n" s="2">
-        <v>67212.63</v>
+        <v>17239.42</v>
       </c>
       <c r="I39" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J39" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K39" t="n" s="0">
-        <v>508.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="F40" t="n" s="5">
-        <v>45957.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G40" t="n" s="2">
-        <v>26594.09</v>
+        <v>24314.25</v>
       </c>
       <c r="H40" t="n" s="2">
-        <v>26594.09</v>
+        <v>24314.25</v>
       </c>
       <c r="I40" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J40" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K40" t="n" s="0">
-        <v>262.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F41" t="n" s="5">
-        <v>46162.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G41" t="n" s="2">
-        <v>16647.61</v>
+        <v>10320.93</v>
       </c>
       <c r="H41" t="n" s="2">
-        <v>0.0</v>
+        <v>4361.61</v>
       </c>
       <c r="I41" t="n" s="2">
-        <v>16647.61</v>
+        <v>5959.32</v>
       </c>
       <c r="J41" t="s" s="0">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n" s="0">
-        <v>57.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="F42" t="n" s="5">
-        <v>46184.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G42" t="n" s="2">
-        <v>71851.88</v>
+        <v>12076.67</v>
       </c>
       <c r="H42" t="n" s="2">
-        <v>71851.88</v>
+        <v>12076.67</v>
       </c>
       <c r="I42" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J42" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K42" t="n" s="0">
-        <v>35.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F43" t="n" s="5">
-        <v>45938.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G43" t="n" s="2">
-        <v>180460.14</v>
+        <v>2314.51</v>
       </c>
       <c r="H43" t="n" s="2">
-        <v>180460.14</v>
+        <v>2314.51</v>
       </c>
       <c r="I43" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J43" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n" s="0">
-        <v>281.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="F44" t="n" s="5">
-        <v>46151.0</v>
+        <v>46214.0</v>
       </c>
       <c r="G44" t="n" s="2">
-        <v>49301.83</v>
+        <v>23451.02</v>
       </c>
       <c r="H44" t="n" s="2">
-        <v>0.0</v>
+        <v>15586.55</v>
       </c>
       <c r="I44" t="n" s="2">
-        <v>49301.83</v>
+        <v>7864.47</v>
       </c>
       <c r="J44" t="s" s="0">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n" s="0">
-        <v>68.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s" s="0">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="F45" t="n" s="5">
-        <v>45865.0</v>
+        <v>46215.0</v>
       </c>
       <c r="G45" t="n" s="2">
-        <v>34177.45</v>
+        <v>6384.04</v>
       </c>
       <c r="H45" t="n" s="2">
-        <v>34177.45</v>
+        <v>6384.04</v>
       </c>
       <c r="I45" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J45" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n" s="0">
-        <v>354.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n" s="5">
-        <v>45771.0</v>
+        <v>46215.0</v>
       </c>
       <c r="G46" t="n" s="2">
-        <v>27195.34</v>
+        <v>8144.97</v>
       </c>
       <c r="H46" t="n" s="2">
-        <v>0.0</v>
+        <v>8144.97</v>
       </c>
       <c r="I46" t="n" s="2">
-        <v>27195.34</v>
+        <v>0.0</v>
       </c>
       <c r="J46" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n" s="0">
-        <v>448.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>187</v>
+        <v>56</v>
       </c>
       <c r="F47" t="n" s="5">
-        <v>45690.0</v>
+        <v>46215.0</v>
       </c>
       <c r="G47" t="n" s="2">
-        <v>49838.4</v>
+        <v>13139.85</v>
       </c>
       <c r="H47" t="n" s="2">
-        <v>49838.4</v>
+        <v>13139.85</v>
       </c>
       <c r="I47" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J47" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K47" t="n" s="0">
-        <v>529.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="F48" t="n" s="5">
-        <v>46054.0</v>
+        <v>46215.0</v>
       </c>
       <c r="G48" t="n" s="2">
-        <v>3924.55</v>
+        <v>7492.53</v>
       </c>
       <c r="H48" t="n" s="2">
-        <v>3924.55</v>
+        <v>0.0</v>
       </c>
       <c r="I48" t="n" s="2">
-        <v>0.0</v>
+        <v>7492.53</v>
       </c>
       <c r="J48" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n" s="0">
-        <v>165.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="F49" t="n" s="5">
-        <v>46165.0</v>
+        <v>46215.0</v>
       </c>
       <c r="G49" t="n" s="2">
-        <v>129854.82</v>
+        <v>20662.4</v>
       </c>
       <c r="H49" t="n" s="2">
-        <v>0.0</v>
+        <v>20662.4</v>
       </c>
       <c r="I49" t="n" s="2">
-        <v>129854.82</v>
+        <v>0.0</v>
       </c>
       <c r="J49" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n" s="0">
-        <v>54.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>202</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>204</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n" s="5">
-        <v>46196.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G50" t="n" s="2">
-        <v>62864.74</v>
+        <v>17059.97</v>
       </c>
       <c r="H50" t="n" s="2">
-        <v>62864.74</v>
+        <v>17059.97</v>
       </c>
       <c r="I50" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J50" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K50" t="n" s="0">
-        <v>23.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="C51" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="D51" t="s" s="0">
-        <v>203</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0"/>
       <c r="E51" t="s" s="0">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="F51" t="n" s="5">
-        <v>45727.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G51" t="n" s="2">
-        <v>176515.58</v>
+        <v>21603.85</v>
       </c>
       <c r="H51" t="n" s="2">
-        <v>176515.58</v>
+        <v>21603.85</v>
       </c>
       <c r="I51" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J51" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K51" t="n" s="0">
-        <v>492.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="F52" t="n" s="5">
-        <v>46169.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G52" t="n" s="2">
-        <v>144686.32</v>
+        <v>17741.19</v>
       </c>
       <c r="H52" t="n" s="2">
-        <v>144686.32</v>
+        <v>17741.19</v>
       </c>
       <c r="I52" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J52" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K52" t="n" s="0">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>213</v>
-      </c>
-      <c r="C53" t="s" s="0">
-        <v>214</v>
-      </c>
-      <c r="D53" t="s" s="0">
-        <v>215</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
       <c r="E53" t="s" s="0">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="F53" t="n" s="5">
-        <v>45948.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G53" t="n" s="2">
-        <v>78286.99</v>
+        <v>22778.75</v>
       </c>
       <c r="H53" t="n" s="2">
-        <v>78286.99</v>
+        <v>13020.9</v>
       </c>
       <c r="I53" t="n" s="2">
-        <v>0.0</v>
+        <v>9757.85</v>
       </c>
       <c r="J53" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K53" t="n" s="0">
-        <v>271.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="E54" t="s" s="0">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="F54" t="n" s="5">
-        <v>46215.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G54" t="n" s="2">
-        <v>82300.05</v>
+        <v>11477.19</v>
       </c>
       <c r="H54" t="n" s="2">
-        <v>82300.05</v>
+        <v>11477.19</v>
       </c>
       <c r="I54" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J54" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n" s="0">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="F55" t="n" s="5">
-        <v>45987.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G55" t="n" s="2">
-        <v>59877.28</v>
+        <v>7340.33</v>
       </c>
       <c r="H55" t="n" s="2">
-        <v>0.0</v>
+        <v>7340.33</v>
       </c>
       <c r="I55" t="n" s="2">
-        <v>59877.28</v>
+        <v>0.0</v>
       </c>
       <c r="J55" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K55" t="n" s="0">
-        <v>232.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="F56" t="n" s="5">
-        <v>45752.0</v>
+        <v>46216.0</v>
       </c>
       <c r="G56" t="n" s="2">
-        <v>107354.64</v>
+        <v>5633.44</v>
       </c>
       <c r="H56" t="n" s="2">
-        <v>107354.64</v>
+        <v>5633.44</v>
       </c>
       <c r="I56" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J56" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n" s="0">
-        <v>467.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="C57" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D57" t="s" s="0">
-        <v>35</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0"/>
       <c r="E57" t="s" s="0">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="F57" t="n" s="5">
-        <v>45758.0</v>
+        <v>46217.0</v>
       </c>
       <c r="G57" t="n" s="2">
-        <v>80079.44</v>
+        <v>24985.59</v>
       </c>
       <c r="H57" t="n" s="2">
-        <v>38821.57</v>
+        <v>24985.59</v>
       </c>
       <c r="I57" t="n" s="2">
-        <v>41257.87</v>
+        <v>0.0</v>
       </c>
       <c r="J57" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K57" t="n" s="0">
-        <v>461.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="C58" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="D58" t="s" s="0">
-        <v>35</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0"/>
       <c r="E58" t="s" s="0">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="F58" t="n" s="5">
-        <v>46190.0</v>
+        <v>46217.0</v>
       </c>
       <c r="G58" t="n" s="2">
-        <v>94526.58</v>
+        <v>19127.38</v>
       </c>
       <c r="H58" t="n" s="2">
-        <v>0.0</v>
+        <v>19127.38</v>
       </c>
       <c r="I58" t="n" s="2">
-        <v>94526.58</v>
+        <v>0.0</v>
       </c>
       <c r="J58" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K58" t="n" s="0">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="F59" t="n" s="5">
-        <v>46183.0</v>
+        <v>46217.0</v>
       </c>
       <c r="G59" t="n" s="2">
-        <v>68231.41</v>
+        <v>20444.44</v>
       </c>
       <c r="H59" t="n" s="2">
-        <v>0.0</v>
+        <v>20444.44</v>
       </c>
       <c r="I59" t="n" s="2">
-        <v>68231.41</v>
+        <v>0.0</v>
       </c>
       <c r="J59" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n" s="0">
-        <v>36.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>235</v>
-      </c>
-      <c r="C60" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="D60" t="s" s="0">
-        <v>237</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
       <c r="E60" t="s" s="0">
-        <v>238</v>
+        <v>101</v>
       </c>
       <c r="F60" t="n" s="5">
-        <v>46068.0</v>
+        <v>46217.0</v>
       </c>
       <c r="G60" t="n" s="2">
-        <v>117280.87</v>
+        <v>16865.83</v>
       </c>
       <c r="H60" t="n" s="2">
-        <v>117280.87</v>
+        <v>0.0</v>
       </c>
       <c r="I60" t="n" s="2">
-        <v>0.0</v>
+        <v>16865.83</v>
       </c>
       <c r="J60" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K60" t="n" s="0">
-        <v>151.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>238</v>
+        <v>117</v>
       </c>
       <c r="F61" t="n" s="5">
-        <v>46023.0</v>
+        <v>46218.0</v>
       </c>
       <c r="G61" t="n" s="2">
-        <v>4964.2</v>
+        <v>21100.87</v>
       </c>
       <c r="H61" t="n" s="2">
-        <v>4964.2</v>
+        <v>21100.87</v>
       </c>
       <c r="I61" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J61" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n" s="0">
-        <v>196.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>236</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="F62" t="n" s="5">
-        <v>46129.0</v>
+        <v>46218.0</v>
       </c>
       <c r="G62" t="n" s="2">
-        <v>70097.8</v>
+        <v>3731.89</v>
       </c>
       <c r="H62" t="n" s="2">
-        <v>70097.8</v>
+        <v>1439.87</v>
       </c>
       <c r="I62" t="n" s="2">
-        <v>0.0</v>
+        <v>2292.02</v>
       </c>
       <c r="J62" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K62" t="n" s="0">
-        <v>90.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>246</v>
+        <v>84</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="F63" t="n" s="5">
-        <v>46002.0</v>
+        <v>46218.0</v>
       </c>
       <c r="G63" t="n" s="2">
-        <v>51570.84</v>
+        <v>15444.88</v>
       </c>
       <c r="H63" t="n" s="2">
-        <v>0.0</v>
+        <v>10802.95</v>
       </c>
       <c r="I63" t="n" s="2">
-        <v>51570.84</v>
+        <v>4641.93</v>
       </c>
       <c r="J63" t="s" s="0">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n" s="0">
-        <v>217.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>251</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>252</v>
+        <v>123</v>
       </c>
       <c r="F64" t="n" s="5">
-        <v>45959.0</v>
+        <v>46218.0</v>
       </c>
       <c r="G64" t="n" s="2">
-        <v>46701.88</v>
+        <v>3453.99</v>
       </c>
       <c r="H64" t="n" s="2">
-        <v>46701.88</v>
+        <v>3453.99</v>
       </c>
       <c r="I64" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J64" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n" s="0">
-        <v>260.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>255</v>
+        <v>151</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>256</v>
+        <v>152</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="F65" t="n" s="5">
-        <v>46160.0</v>
+        <v>46218.0</v>
       </c>
       <c r="G65" t="n" s="2">
-        <v>74549.05</v>
+        <v>23835.76</v>
       </c>
       <c r="H65" t="n" s="2">
-        <v>74549.05</v>
+        <v>23835.76</v>
       </c>
       <c r="I65" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J65" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n" s="0">
-        <v>59.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>260</v>
+        <v>27</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>261</v>
+        <v>28</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="F66" t="n" s="5">
-        <v>45877.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G66" t="n" s="2">
-        <v>81689.71</v>
+        <v>23598.22</v>
       </c>
       <c r="H66" t="n" s="2">
-        <v>81689.71</v>
+        <v>0.0</v>
       </c>
       <c r="I66" t="n" s="2">
-        <v>0.0</v>
+        <v>23598.22</v>
       </c>
       <c r="J66" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K66" t="n" s="0">
-        <v>342.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>260</v>
+        <v>27</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>261</v>
+        <v>28</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n" s="5">
-        <v>45793.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G67" t="n" s="2">
-        <v>116006.99</v>
+        <v>2491.22</v>
       </c>
       <c r="H67" t="n" s="2">
-        <v>69216.34</v>
+        <v>0.0</v>
       </c>
       <c r="I67" t="n" s="2">
-        <v>46790.65</v>
+        <v>2491.22</v>
       </c>
       <c r="J67" t="s" s="0">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K67" t="n" s="0">
-        <v>426.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>267</v>
+        <v>59</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="F68" t="n" s="5">
-        <v>46171.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G68" t="n" s="2">
-        <v>163107.33</v>
+        <v>15486.81</v>
       </c>
       <c r="H68" t="n" s="2">
-        <v>163107.33</v>
+        <v>0.0</v>
       </c>
       <c r="I68" t="n" s="2">
-        <v>0.0</v>
+        <v>15486.81</v>
       </c>
       <c r="J68" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n" s="0">
-        <v>48.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>267</v>
+        <v>39</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="F69" t="n" s="5">
-        <v>45862.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G69" t="n" s="2">
-        <v>26405.87</v>
+        <v>4989.82</v>
       </c>
       <c r="H69" t="n" s="2">
-        <v>26405.87</v>
+        <v>0.0</v>
       </c>
       <c r="I69" t="n" s="2">
-        <v>0.0</v>
+        <v>4989.82</v>
       </c>
       <c r="J69" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n" s="0">
-        <v>357.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>47</v>
+        <v>225</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="F70" t="n" s="5">
-        <v>45825.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G70" t="n" s="2">
-        <v>97598.1</v>
+        <v>15543.62</v>
       </c>
       <c r="H70" t="n" s="2">
-        <v>97598.1</v>
+        <v>9074.62</v>
       </c>
       <c r="I70" t="n" s="2">
-        <v>0.0</v>
+        <v>6469.0</v>
       </c>
       <c r="J70" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K70" t="n" s="0">
-        <v>394.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>277</v>
+        <v>67</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>278</v>
+        <v>68</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>279</v>
+        <v>69</v>
       </c>
       <c r="F71" t="n" s="5">
-        <v>46007.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G71" t="n" s="2">
-        <v>118239.48</v>
+        <v>12953.66</v>
       </c>
       <c r="H71" t="n" s="2">
-        <v>118239.48</v>
+        <v>0.0</v>
       </c>
       <c r="I71" t="n" s="2">
-        <v>0.0</v>
+        <v>12953.66</v>
       </c>
       <c r="J71" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n" s="0">
-        <v>212.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="F72" t="n" s="5">
-        <v>45903.0</v>
+        <v>46219.0</v>
       </c>
       <c r="G72" t="n" s="2">
-        <v>93038.2</v>
+        <v>20014.22</v>
       </c>
       <c r="H72" t="n" s="2">
-        <v>93038.2</v>
+        <v>0.0</v>
       </c>
       <c r="I72" t="n" s="2">
-        <v>0.0</v>
+        <v>20014.22</v>
       </c>
       <c r="J72" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K72" t="n" s="0">
-        <v>316.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>284</v>
+        <v>142</v>
       </c>
       <c r="F73" t="n" s="5">
-        <v>45699.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G73" t="n" s="2">
-        <v>47187.96</v>
+        <v>18385.23</v>
       </c>
       <c r="H73" t="n" s="2">
-        <v>47187.96</v>
+        <v>12335.2</v>
       </c>
       <c r="I73" t="n" s="2">
-        <v>0.0</v>
+        <v>6050.03</v>
       </c>
       <c r="J73" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K73" t="n" s="0">
-        <v>520.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>179</v>
+        <v>39</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="F74" t="n" s="5">
-        <v>46075.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G74" t="n" s="2">
-        <v>22781.21</v>
+        <v>4281.1</v>
       </c>
       <c r="H74" t="n" s="2">
-        <v>22781.21</v>
+        <v>2155.54</v>
       </c>
       <c r="I74" t="n" s="2">
-        <v>0.0</v>
+        <v>2125.56</v>
       </c>
       <c r="J74" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K74" t="n" s="0">
-        <v>144.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>289</v>
+        <v>120</v>
       </c>
       <c r="F75" t="n" s="5">
-        <v>45775.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G75" t="n" s="2">
-        <v>63174.97</v>
+        <v>11517.71</v>
       </c>
       <c r="H75" t="n" s="2">
-        <v>63174.97</v>
+        <v>0.0</v>
       </c>
       <c r="I75" t="n" s="2">
-        <v>0.0</v>
+        <v>11517.71</v>
       </c>
       <c r="J75" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K75" t="n" s="0">
-        <v>444.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>289</v>
+        <v>153</v>
       </c>
       <c r="F76" t="n" s="5">
-        <v>46090.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G76" t="n" s="2">
-        <v>92337.19</v>
+        <v>23932.63</v>
       </c>
       <c r="H76" t="n" s="2">
-        <v>92337.19</v>
+        <v>9446.08</v>
       </c>
       <c r="I76" t="n" s="2">
-        <v>0.0</v>
+        <v>14486.55</v>
       </c>
       <c r="J76" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K76" t="n" s="0">
-        <v>129.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>289</v>
+        <v>142</v>
       </c>
       <c r="F77" t="n" s="5">
-        <v>45840.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G77" t="n" s="2">
-        <v>103162.3</v>
+        <v>22092.97</v>
       </c>
       <c r="H77" t="n" s="2">
-        <v>103162.3</v>
+        <v>22092.97</v>
       </c>
       <c r="I77" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J77" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K77" t="n" s="0">
-        <v>379.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>296</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>297</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>298</v>
+        <v>137</v>
       </c>
       <c r="F78" t="n" s="5">
-        <v>45967.0</v>
+        <v>46220.0</v>
       </c>
       <c r="G78" t="n" s="2">
-        <v>35091.64</v>
+        <v>6892.99</v>
       </c>
       <c r="H78" t="n" s="2">
-        <v>35091.64</v>
+        <v>6892.99</v>
       </c>
       <c r="I78" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J78" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K78" t="n" s="0">
-        <v>252.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>296</v>
+        <v>59</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>297</v>
+        <v>60</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>298</v>
+        <v>120</v>
       </c>
       <c r="F79" t="n" s="5">
-        <v>45685.0</v>
+        <v>46221.0</v>
       </c>
       <c r="G79" t="n" s="2">
-        <v>3067.33</v>
+        <v>17949.84</v>
       </c>
       <c r="H79" t="n" s="2">
-        <v>3067.33</v>
+        <v>6003.97</v>
       </c>
       <c r="I79" t="n" s="2">
-        <v>0.0</v>
+        <v>11945.87</v>
       </c>
       <c r="J79" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K79" t="n" s="0">
-        <v>534.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>301</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>304</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>305</v>
+        <v>72</v>
       </c>
       <c r="F80" t="n" s="5">
-        <v>46107.0</v>
+        <v>46221.0</v>
       </c>
       <c r="G80" t="n" s="2">
-        <v>67628.51</v>
+        <v>19867.22</v>
       </c>
       <c r="H80" t="n" s="2">
-        <v>67628.51</v>
+        <v>19867.22</v>
       </c>
       <c r="I80" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J80" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K80" t="n" s="0">
-        <v>112.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>303</v>
+        <v>33</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="F81" t="n" s="5">
-        <v>45818.0</v>
+        <v>46221.0</v>
       </c>
       <c r="G81" t="n" s="2">
-        <v>208725.67</v>
+        <v>17224.59</v>
       </c>
       <c r="H81" t="n" s="2">
-        <v>208725.67</v>
+        <v>17224.59</v>
       </c>
       <c r="I81" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J81" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K81" t="n" s="0">
-        <v>401.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>310</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n" s="5">
-        <v>46159.0</v>
+        <v>46221.0</v>
       </c>
       <c r="G82" t="n" s="2">
-        <v>75910.22</v>
+        <v>17599.01</v>
       </c>
       <c r="H82" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="I82" t="n" s="2">
-        <v>75910.22</v>
+        <v>17599.01</v>
       </c>
       <c r="J82" t="s" s="0">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K82" t="n" s="0">
-        <v>60.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>310</v>
+        <v>69</v>
       </c>
       <c r="F83" t="n" s="5">
-        <v>45881.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G83" t="n" s="2">
-        <v>28596.07</v>
+        <v>13439.86</v>
       </c>
       <c r="H83" t="n" s="2">
-        <v>28596.07</v>
+        <v>13439.86</v>
       </c>
       <c r="I83" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J83" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K83" t="n" s="0">
-        <v>338.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>158</v>
+        <v>261</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="F84" t="n" s="5">
-        <v>46120.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G84" t="n" s="2">
-        <v>97807.19</v>
+        <v>20542.6</v>
       </c>
       <c r="H84" t="n" s="2">
-        <v>97807.19</v>
+        <v>9860.24</v>
       </c>
       <c r="I84" t="n" s="2">
-        <v>0.0</v>
+        <v>10682.36</v>
       </c>
       <c r="J84" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K84" t="n" s="0">
-        <v>99.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>316</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="F85" t="n" s="5">
-        <v>45908.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G85" t="n" s="2">
-        <v>103110.48</v>
+        <v>9200.39</v>
       </c>
       <c r="H85" t="n" s="2">
-        <v>103110.48</v>
+        <v>9200.39</v>
       </c>
       <c r="I85" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J85" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K85" t="n" s="0">
-        <v>311.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>320</v>
+        <v>77</v>
       </c>
       <c r="F86" t="n" s="5">
-        <v>45993.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G86" t="n" s="2">
-        <v>5395.59</v>
+        <v>5953.08</v>
       </c>
       <c r="H86" t="n" s="2">
-        <v>5395.59</v>
+        <v>2093.18</v>
       </c>
       <c r="I86" t="n" s="2">
-        <v>0.0</v>
+        <v>3859.9</v>
       </c>
       <c r="J86" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K86" t="n" s="0">
-        <v>226.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>324</v>
-      </c>
-      <c r="C87" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="D87" t="s" s="0">
-        <v>68</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="C87" s="0"/>
+      <c r="D87" s="0"/>
       <c r="E87" t="s" s="0">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="F87" t="n" s="5">
-        <v>45805.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G87" t="n" s="2">
-        <v>56031.33</v>
+        <v>15544.04</v>
       </c>
       <c r="H87" t="n" s="2">
-        <v>56031.33</v>
+        <v>0.0</v>
       </c>
       <c r="I87" t="n" s="2">
-        <v>0.0</v>
+        <v>15544.04</v>
       </c>
       <c r="J87" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K87" t="n" s="0">
-        <v>414.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>325</v>
+        <v>90</v>
       </c>
       <c r="F88" t="n" s="5">
-        <v>46159.0</v>
+        <v>46222.0</v>
       </c>
       <c r="G88" t="n" s="2">
-        <v>66966.29</v>
+        <v>3756.73</v>
       </c>
       <c r="H88" t="n" s="2">
-        <v>66966.29</v>
+        <v>3756.73</v>
       </c>
       <c r="I88" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J88" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K88" t="n" s="0">
-        <v>60.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>331</v>
+        <v>111</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>332</v>
+        <v>112</v>
       </c>
       <c r="F89" t="n" s="5">
-        <v>46064.0</v>
+        <v>46223.0</v>
       </c>
       <c r="G89" t="n" s="2">
-        <v>51643.75</v>
+        <v>6537.25</v>
       </c>
       <c r="H89" t="n" s="2">
-        <v>51643.75</v>
+        <v>6537.25</v>
       </c>
       <c r="I89" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J89" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K89" t="n" s="0">
-        <v>155.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>334</v>
+        <v>275</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>331</v>
+        <v>22</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>332</v>
+        <v>23</v>
       </c>
       <c r="F90" t="n" s="5">
-        <v>46042.0</v>
+        <v>46223.0</v>
       </c>
       <c r="G90" t="n" s="2">
-        <v>74894.11</v>
+        <v>15327.77</v>
       </c>
       <c r="H90" t="n" s="2">
-        <v>74894.11</v>
+        <v>0.0</v>
       </c>
       <c r="I90" t="n" s="2">
-        <v>0.0</v>
+        <v>15327.77</v>
       </c>
       <c r="J90" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K90" t="n" s="0">
-        <v>177.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>336</v>
+        <v>277</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>337</v>
+        <v>27</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>339</v>
+        <v>29</v>
       </c>
       <c r="F91" t="n" s="5">
-        <v>46210.0</v>
+        <v>46223.0</v>
       </c>
       <c r="G91" t="n" s="2">
-        <v>12705.59</v>
+        <v>20315.58</v>
       </c>
       <c r="H91" t="n" s="2">
-        <v>12705.59</v>
+        <v>20315.58</v>
       </c>
       <c r="I91" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J91" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K91" t="n" s="0">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>340</v>
+        <v>278</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>341</v>
-      </c>
-      <c r="C92" t="s" s="0">
-        <v>337</v>
-      </c>
-      <c r="D92" t="s" s="0">
-        <v>338</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C92" s="0"/>
+      <c r="D92" s="0"/>
       <c r="E92" t="s" s="0">
-        <v>339</v>
+        <v>107</v>
       </c>
       <c r="F92" t="n" s="5">
-        <v>46185.0</v>
+        <v>46223.0</v>
       </c>
       <c r="G92" t="n" s="2">
-        <v>78115.48</v>
+        <v>20211.81</v>
       </c>
       <c r="H92" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="I92" t="n" s="2">
-        <v>78115.48</v>
+        <v>20211.81</v>
       </c>
       <c r="J92" t="s" s="0">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K92" t="n" s="0">
-        <v>34.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>342</v>
+        <v>280</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>343</v>
+        <v>281</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>344</v>
+        <v>117</v>
       </c>
       <c r="F93" t="n" s="5">
-        <v>45839.0</v>
+        <v>46224.0</v>
       </c>
       <c r="G93" t="n" s="2">
-        <v>138565.65</v>
+        <v>12362.03</v>
       </c>
       <c r="H93" t="n" s="2">
-        <v>138565.65</v>
+        <v>12362.03</v>
       </c>
       <c r="I93" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J93" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K93" t="n" s="0">
-        <v>380.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>348</v>
+        <v>40</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>349</v>
+        <v>284</v>
       </c>
       <c r="F94" t="n" s="5">
-        <v>46174.0</v>
+        <v>46224.0</v>
       </c>
       <c r="G94" t="n" s="2">
-        <v>48507.13</v>
+        <v>14053.58</v>
       </c>
       <c r="H94" t="n" s="2">
-        <v>48507.13</v>
+        <v>14053.58</v>
       </c>
       <c r="I94" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J94" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K94" t="n" s="0">
-        <v>45.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>350</v>
+        <v>285</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>351</v>
+        <v>286</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>347</v>
+        <v>135</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>348</v>
+        <v>136</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>349</v>
+        <v>137</v>
       </c>
       <c r="F95" t="n" s="5">
-        <v>45923.0</v>
+        <v>46224.0</v>
       </c>
       <c r="G95" t="n" s="2">
-        <v>168628.49</v>
+        <v>3204.41</v>
       </c>
       <c r="H95" t="n" s="2">
-        <v>168628.49</v>
+        <v>1081.08</v>
       </c>
       <c r="I95" t="n" s="2">
-        <v>0.0</v>
+        <v>2123.33</v>
       </c>
       <c r="J95" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K95" t="n" s="0">
-        <v>296.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>347</v>
+        <v>59</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>348</v>
+        <v>60</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>349</v>
+        <v>120</v>
       </c>
       <c r="F96" t="n" s="5">
-        <v>46113.0</v>
+        <v>46224.0</v>
       </c>
       <c r="G96" t="n" s="2">
-        <v>25159.85</v>
+        <v>17100.97</v>
       </c>
       <c r="H96" t="n" s="2">
-        <v>25159.85</v>
+        <v>17100.97</v>
       </c>
       <c r="I96" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J96" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K96" t="n" s="0">
-        <v>106.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>355</v>
-      </c>
-      <c r="C97" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="D97" t="s" s="0">
-        <v>357</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C97" s="0"/>
+      <c r="D97" s="0"/>
       <c r="E97" t="s" s="0">
-        <v>358</v>
+        <v>107</v>
       </c>
       <c r="F97" t="n" s="5">
-        <v>45990.0</v>
+        <v>46224.0</v>
       </c>
       <c r="G97" t="n" s="2">
-        <v>70407.79</v>
+        <v>4939.26</v>
       </c>
       <c r="H97" t="n" s="2">
-        <v>70407.79</v>
+        <v>4939.26</v>
       </c>
       <c r="I97" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J97" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K97" t="n" s="0">
-        <v>229.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>357</v>
+        <v>261</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="F98" t="n" s="5">
-        <v>46019.0</v>
+        <v>46225.0</v>
       </c>
       <c r="G98" t="n" s="2">
-        <v>50178.32</v>
+        <v>16214.72</v>
       </c>
       <c r="H98" t="n" s="2">
-        <v>50178.32</v>
+        <v>0.0</v>
       </c>
       <c r="I98" t="n" s="2">
-        <v>0.0</v>
+        <v>16214.72</v>
       </c>
       <c r="J98" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K98" t="n" s="0">
-        <v>200.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>361</v>
+        <v>293</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>363</v>
+        <v>193</v>
       </c>
       <c r="F99" t="n" s="5">
-        <v>46050.0</v>
+        <v>46225.0</v>
       </c>
       <c r="G99" t="n" s="2">
-        <v>136879.45</v>
+        <v>10378.89</v>
       </c>
       <c r="H99" t="n" s="2">
-        <v>136879.45</v>
+        <v>10378.89</v>
       </c>
       <c r="I99" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J99" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K99" t="n" s="0">
-        <v>169.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>364</v>
+        <v>295</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>366</v>
+        <v>232</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>367</v>
+        <v>233</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>368</v>
+        <v>234</v>
       </c>
       <c r="F100" t="n" s="5">
-        <v>46068.0</v>
+        <v>46225.0</v>
       </c>
       <c r="G100" t="n" s="2">
-        <v>154377.69</v>
+        <v>12787.36</v>
       </c>
       <c r="H100" t="n" s="2">
-        <v>154377.69</v>
+        <v>12787.36</v>
       </c>
       <c r="I100" t="n" s="2">
         <v>0.0</v>
       </c>
       <c r="J100" t="s" s="0">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K100" t="n" s="0">
-        <v>151.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>369</v>
+        <v>297</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>370</v>
+        <v>298</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>371</v>
+        <v>232</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>372</v>
+        <v>233</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>373</v>
+        <v>234</v>
       </c>
       <c r="F101" t="n" s="5">
-        <v>46041.0</v>
+        <v>46225.0</v>
       </c>
       <c r="G101" t="n" s="2">
-        <v>56676.31</v>
+        <v>11629.2</v>
       </c>
       <c r="H101" t="n" s="2">
-        <v>56676.31</v>
+        <v>7056.41</v>
       </c>
       <c r="I101" t="n" s="2">
-        <v>0.0</v>
+        <v>4572.79</v>
       </c>
       <c r="J101" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K101" t="n" s="0">
-        <v>178.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>374</v>
+        <v>299</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>375</v>
-      </c>
-      <c r="C102" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="D102" t="s" s="0">
-        <v>377</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C102" s="0"/>
+      <c r="D102" s="0"/>
       <c r="E102" t="s" s="0">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="F102" t="n" s="5">
-        <v>45837.0</v>
+        <v>46226.0</v>
       </c>
       <c r="G102" t="n" s="2">
-        <v>95292.66</v>
+        <v>4359.56</v>
       </c>
       <c r="H102" t="n" s="2">
-        <v>95292.66</v>
+        <v>1360.68</v>
       </c>
       <c r="I102" t="n" s="2">
-        <v>0.0</v>
+        <v>2998.88</v>
       </c>
       <c r="J102" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K102" t="n" s="0">
-        <v>382.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>379</v>
+        <v>301</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>380</v>
-      </c>
-      <c r="C103" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="D103" t="s" s="0">
-        <v>198</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C103" s="0"/>
+      <c r="D103" s="0"/>
       <c r="E103" t="s" s="0">
-        <v>381</v>
+        <v>107</v>
       </c>
       <c r="F103" t="n" s="5">
-        <v>46185.0</v>
+        <v>46226.0</v>
       </c>
       <c r="G103" t="n" s="2">
-        <v>172349.5</v>
+        <v>11542.63</v>
       </c>
       <c r="H103" t="n" s="2">
-        <v>172349.5</v>
+        <v>4857.57</v>
       </c>
       <c r="I103" t="n" s="2">
-        <v>0.0</v>
+        <v>6685.06</v>
       </c>
       <c r="J103" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K103" t="n" s="0">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="B104" t="s" s="0">
-        <v>383</v>
-      </c>
-      <c r="C104" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="D104" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="E104" t="s" s="0">
-        <v>384</v>
-      </c>
-      <c r="F104" t="n" s="5">
-        <v>46124.0</v>
-      </c>
-      <c r="G104" t="n" s="2">
-        <v>146973.9</v>
-      </c>
-      <c r="H104" t="n" s="2">
-        <v>48871.28</v>
-      </c>
-      <c r="I104" t="n" s="2">
-        <v>98102.62</v>
-      </c>
-      <c r="J104" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="K104" t="n" s="0">
-        <v>95.0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="0">
-        <v>385</v>
-      </c>
-      <c r="B105" t="s" s="0">
-        <v>386</v>
-      </c>
-      <c r="C105" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="D105" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="E105" t="s" s="0">
-        <v>384</v>
-      </c>
-      <c r="F105" t="n" s="5">
-        <v>45852.0</v>
-      </c>
-      <c r="G105" t="n" s="2">
-        <v>84002.25</v>
-      </c>
-      <c r="H105" t="n" s="2">
-        <v>84002.25</v>
-      </c>
-      <c r="I105" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J105" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="K105" t="n" s="0">
-        <v>367.0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="0">
-        <v>387</v>
-      </c>
-      <c r="B106" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="C106" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="D106" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="E106" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="F106" t="n" s="5">
-        <v>45839.0</v>
-      </c>
-      <c r="G106" t="n" s="2">
-        <v>112554.66</v>
-      </c>
-      <c r="H106" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I106" t="n" s="2">
-        <v>112554.66</v>
-      </c>
-      <c r="J106" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="K106" t="n" s="0">
-        <v>380.0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="B107" t="s" s="0">
-        <v>391</v>
-      </c>
-      <c r="C107" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="D107" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="E107" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="F107" t="n" s="5">
-        <v>45898.0</v>
-      </c>
-      <c r="G107" t="n" s="2">
-        <v>68619.71</v>
-      </c>
-      <c r="H107" t="n" s="2">
-        <v>68619.71</v>
-      </c>
-      <c r="I107" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J107" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="K107" t="n" s="0">
-        <v>321.0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="0">
-        <v>392</v>
-      </c>
-      <c r="B108" t="s" s="0">
-        <v>393</v>
-      </c>
-      <c r="C108" t="s" s="0">
-        <v>394</v>
-      </c>
-      <c r="D108" t="s" s="0">
-        <v>395</v>
-      </c>
-      <c r="E108" t="s" s="0">
-        <v>396</v>
-      </c>
-      <c r="F108" t="n" s="5">
-        <v>46001.0</v>
-      </c>
-      <c r="G108" t="n" s="2">
-        <v>21687.44</v>
-      </c>
-      <c r="H108" t="n" s="2">
-        <v>21687.44</v>
-      </c>
-      <c r="I108" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J108" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="K108" t="n" s="0">
-        <v>218.0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="0">
-        <v>397</v>
-      </c>
-      <c r="B109" t="s" s="0">
-        <v>398</v>
-      </c>
-      <c r="C109" t="s" s="0">
-        <v>399</v>
-      </c>
-      <c r="D109" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="E109" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="F109" t="n" s="5">
-        <v>46049.0</v>
-      </c>
-      <c r="G109" t="n" s="2">
-        <v>66025.68</v>
-      </c>
-      <c r="H109" t="n" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I109" t="n" s="2">
-        <v>66025.68</v>
-      </c>
-      <c r="J109" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="K109" t="n" s="0">
-        <v>170.0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="4">
-        <v>402</v>
-      </c>
-      <c r="G110" t="n" s="3">
-        <v>9279111.840000005</v>
-      </c>
-      <c r="H110" t="n" s="3">
-        <v>7765263.280000002</v>
-      </c>
-      <c r="I110" t="n" s="3">
-        <v>1513848.5599999996</v>
+      <c r="A104" t="s" s="4">
+        <v>303</v>
+      </c>
+      <c r="G104" t="n" s="3">
+        <v>1406146.1299999997</v>
+      </c>
+      <c r="H104" t="n" s="3">
+        <v>957345.3199999993</v>
+      </c>
+      <c r="I104" t="n" s="3">
+        <v>448800.81000000006</v>
       </c>
     </row>
   </sheetData>
@@ -5309,20 +4721,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.28125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.11328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="9.6796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.99609375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>403</v>
+        <v>304</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>6</v>
@@ -5330,57 +4742,24 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>405</v>
+        <v>306</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>1.0</v>
+        <v>47.0</v>
       </c>
       <c r="C2" t="n" s="2">
-        <v>94526.58</v>
+        <v>448800.81</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>406</v>
-      </c>
-      <c r="B3" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C3" t="n" s="2">
-        <v>466232.09</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>407</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="C4" t="n" s="2">
-        <v>49301.83</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="B5" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="C5" t="n" s="2">
-        <v>903788.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="4">
-        <v>402</v>
-      </c>
-      <c r="B6" t="n" s="4">
-        <v>23.0</v>
-      </c>
-      <c r="C6" t="n" s="3">
-        <v>1513848.56</v>
+      <c r="A3" t="s" s="4">
+        <v>303</v>
+      </c>
+      <c r="B3" t="n" s="4">
+        <v>47.0</v>
+      </c>
+      <c r="C3" t="n" s="3">
+        <v>448800.81</v>
       </c>
     </row>
   </sheetData>
@@ -5395,73 +4774,73 @@
   <cols>
     <col min="1" max="1" width="13.875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>409</v>
+        <v>307</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>411</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>412</v>
+        <v>310</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>37.0</v>
+        <v>26.0</v>
       </c>
       <c r="C2" t="n" s="2">
-        <v>2522375.45</v>
+        <v>301964.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>413</v>
+        <v>311</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>32.0</v>
+        <v>23.0</v>
       </c>
       <c r="C3" t="n" s="2">
-        <v>2421154.12</v>
+        <v>243711.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="C4" t="n" s="2">
-        <v>1438776.03</v>
+        <v>241626.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>415</v>
+        <v>313</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>23.0</v>
+        <v>14.0</v>
       </c>
       <c r="C5" t="n" s="2">
-        <v>1382957.68</v>
+        <v>170042.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>402</v>
+        <v>303</v>
       </c>
       <c r="B6" t="n" s="4">
-        <v>110.0</v>
+        <v>82.0</v>
       </c>
       <c r="C6" t="n" s="3">
-        <v>7765263.28</v>
+        <v>957345.32</v>
       </c>
     </row>
   </sheetData>
@@ -5486,10 +4865,10 @@
         <v>10</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>416</v>
+        <v>314</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>2</v>
@@ -5500,7 +4879,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>418</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -5519,58 +4898,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>419</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>420</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>421</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>422</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>424</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>425</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>426</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>427</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>428</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
-        <v>429</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>430</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>432</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
@@ -5578,20 +4957,20 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>433</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>435</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="1">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>1</v>
@@ -5599,10 +4978,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="1">
-        <v>436</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>437</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
